--- a/myprojects/ACCA-FM/AFM_ACCA.xlsx
+++ b/myprojects/ACCA-FM/AFM_ACCA.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Documents\GitHub\inakm.github.io\myprojects\ACCA-FM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A40AD7E-1A62-4FEA-972A-A7346B4C5E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C5ABB-4D14-4D68-835F-39C5B7C4064A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="5" xr2:uid="{17C56D3C-802C-4E22-A60F-3BA2A8EE22EF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{17C56D3C-802C-4E22-A60F-3BA2A8EE22EF}"/>
   </bookViews>
   <sheets>
-    <sheet name="TYU 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Chp 13 TYU 1" sheetId="1" r:id="rId1"/>
     <sheet name="Answer 1" sheetId="2" r:id="rId2"/>
     <sheet name="TYU 2" sheetId="3" r:id="rId3"/>
     <sheet name="Answer 2" sheetId="4" r:id="rId4"/>
     <sheet name="TYU 3" sheetId="5" r:id="rId5"/>
     <sheet name="Answer 3" sheetId="6" r:id="rId6"/>
+    <sheet name="Chp 14 TYU 1" sheetId="7" r:id="rId7"/>
+    <sheet name="Chp 14 TYU 5" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="145">
   <si>
     <r>
       <t xml:space="preserve">A company is preparing a free cash flow forecast in order to calculate the value of equity.
@@ -279,17 +281,254 @@
   <si>
     <t>Net Present Value</t>
   </si>
+  <si>
+    <t>The following shows the balance sheet (statement of financial position) and statement of profit or loss for Zed Manufacturing for the years ended 31 December 20X7 and 31 December 20X8:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summarised statement of profit or loss ($m) </t>
+  </si>
+  <si>
+    <t>Particulars</t>
+  </si>
+  <si>
+    <t>20X7</t>
+  </si>
+  <si>
+    <t>20X8</t>
+  </si>
+  <si>
+    <t>Sales Revenue</t>
+  </si>
+  <si>
+    <t>Cost of Sales</t>
+  </si>
+  <si>
+    <t>Operating Exp</t>
+  </si>
+  <si>
+    <t>Interet Exp</t>
+  </si>
+  <si>
+    <t>Tax (50%)</t>
+  </si>
+  <si>
+    <t>Summarised statement of financial position (balance sheet) ($m)</t>
+  </si>
+  <si>
+    <t>Gross Profit</t>
+  </si>
+  <si>
+    <t>Profit after Tax (PAT)</t>
+  </si>
+  <si>
+    <t>Intanglible Assets</t>
+  </si>
+  <si>
+    <t>Tanglible Assets at NBV</t>
+  </si>
+  <si>
+    <t>Non-Current Assets:</t>
+  </si>
+  <si>
+    <t>Current Assets:</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Recivables</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Total Assets</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>Share Capital</t>
+  </si>
+  <si>
+    <t>Retained Earnings</t>
+  </si>
+  <si>
+    <t>Non-Current Liabilities:</t>
+  </si>
+  <si>
+    <t>Long-term loans</t>
+  </si>
+  <si>
+    <t>Current Liabilities:</t>
+  </si>
+  <si>
+    <t>Payables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total equity and liabilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required:
+Summarise the performance of Zed Manufacturing in 20X8 compared with 20X7. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance analysis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROCE (based on pre-tax operating profit) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROCE (based on post-tax operating profit) </t>
+  </si>
+  <si>
+    <t>Profitability ratios:</t>
+  </si>
+  <si>
+    <t>Liquidity ratios:</t>
+  </si>
+  <si>
+    <t>Debtor Days</t>
+  </si>
+  <si>
+    <t>Creditor Days</t>
+  </si>
+  <si>
+    <t>Inventory Holding Period</t>
+  </si>
+  <si>
+    <t>Cash Operating Cycle</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change </t>
+  </si>
+  <si>
+    <t>Gearing ratios:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt/Equity </t>
+  </si>
+  <si>
+    <t>Interest expense</t>
+  </si>
+  <si>
+    <t>times</t>
+  </si>
+  <si>
+    <t>Market ratios:</t>
+  </si>
+  <si>
+    <t>Share Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/E ratio </t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>Number of Shares</t>
+  </si>
+  <si>
+    <t>shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire Construction Case Study </t>
+  </si>
+  <si>
+    <t>Wire Construction has suffered from losses in the last three years. Its statement of financial position as at 31 December 20X1 shows:</t>
+  </si>
+  <si>
+    <t>20XX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land and buildings </t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>Non-current assets:</t>
+  </si>
+  <si>
+    <t>Current assets:</t>
+  </si>
+  <si>
+    <t>Receivables</t>
+  </si>
+  <si>
+    <t>Equity and liabilities:</t>
+  </si>
+  <si>
+    <t>Ordinary shares – $1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5% Cumulative preference shares – $1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit and loss </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-current liabilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8% Debenture 20X4 </t>
+  </si>
+  <si>
+    <t>Current liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade payables </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest payable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overdraft </t>
+  </si>
+  <si>
+    <t>Current Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position of interested parties in a liquidation (assuming assets can be sold at going concern value) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Current Value of Assets </t>
+  </si>
+  <si>
+    <t>Debentures</t>
+  </si>
+  <si>
+    <t>Other Creditors:</t>
+  </si>
+  <si>
+    <t>Secured debts:</t>
+  </si>
+  <si>
+    <t>Left for Share Holders</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,8 +551,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,8 +616,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -680,12 +952,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -757,14 +1110,60 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="8" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="8" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -776,9 +1175,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -793,22 +1189,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1201,186 +1626,186 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="62"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="108"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="110"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="110"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="63"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="65"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="110"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="63"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="65"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="110"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="63"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="65"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="105"/>
+      <c r="N7" s="110"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="63"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="65"/>
+      <c r="B8" s="109"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="110"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="63"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="65"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="110"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="63"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="65"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="110"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="63"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="65"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="110"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="63"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="105"/>
+      <c r="N12" s="110"/>
     </row>
     <row r="13" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="67"/>
-      <c r="M13" s="67"/>
-      <c r="N13" s="68"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="113"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
@@ -1689,12 +2114,12 @@
       <c r="C2" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="59"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="116"/>
       <c r="H2" s="35" t="s">
         <v>3</v>
       </c>
@@ -1732,27 +2157,27 @@
         <v>5</v>
       </c>
       <c r="C4" s="7">
-        <f>'TYU 1'!C15</f>
+        <f>'Chp 13 TYU 1'!C15</f>
         <v>500</v>
       </c>
       <c r="D4" s="20">
-        <f>C4*(1+'TYU 1'!D18)</f>
+        <f>C4*(1+'Chp 13 TYU 1'!D18)</f>
         <v>540</v>
       </c>
       <c r="E4" s="7">
-        <f>D4*(1+'TYU 1'!E18)</f>
+        <f>D4*(1+'Chp 13 TYU 1'!E18)</f>
         <v>572.4</v>
       </c>
       <c r="F4" s="7">
-        <f>E4*(1+'TYU 1'!F18)</f>
+        <f>E4*(1+'Chp 13 TYU 1'!F18)</f>
         <v>595.29600000000005</v>
       </c>
       <c r="G4" s="15">
-        <f>F4*(1+'TYU 1'!G18)</f>
+        <f>F4*(1+'Chp 13 TYU 1'!G18)</f>
         <v>607.20192000000009</v>
       </c>
       <c r="H4" s="26">
-        <f>G4*(1+'TYU 1'!H18)</f>
+        <f>G4*(1+'Chp 13 TYU 1'!H18)</f>
         <v>607.20192000000009</v>
       </c>
     </row>
@@ -1761,23 +2186,23 @@
         <v>11</v>
       </c>
       <c r="D5" s="21">
-        <f>D4*'TYU 1'!D19</f>
+        <f>D4*'Chp 13 TYU 1'!D19</f>
         <v>54</v>
       </c>
       <c r="E5" s="6">
-        <f>E4*'TYU 1'!E19</f>
+        <f>E4*'Chp 13 TYU 1'!E19</f>
         <v>57.24</v>
       </c>
       <c r="F5" s="6">
-        <f>F4*'TYU 1'!F19</f>
+        <f>F4*'Chp 13 TYU 1'!F19</f>
         <v>71.435519999999997</v>
       </c>
       <c r="G5" s="16">
-        <f>G4*'TYU 1'!G19</f>
+        <f>G4*'Chp 13 TYU 1'!G19</f>
         <v>72.864230400000011</v>
       </c>
       <c r="H5" s="25">
-        <f>H4*'TYU 1'!H19</f>
+        <f>H4*'Chp 13 TYU 1'!H19</f>
         <v>72.864230400000011</v>
       </c>
     </row>
@@ -1786,23 +2211,23 @@
         <v>12</v>
       </c>
       <c r="D6" s="21">
-        <f>-D5*'TYU 1'!$F$15</f>
+        <f>-D5*'Chp 13 TYU 1'!$F$15</f>
         <v>-16.2</v>
       </c>
       <c r="E6" s="6">
-        <f>-E5*'TYU 1'!$F$15</f>
+        <f>-E5*'Chp 13 TYU 1'!$F$15</f>
         <v>-17.172000000000001</v>
       </c>
       <c r="F6" s="6">
-        <f>-F5*'TYU 1'!$F$15</f>
+        <f>-F5*'Chp 13 TYU 1'!$F$15</f>
         <v>-21.430655999999999</v>
       </c>
       <c r="G6" s="16">
-        <f>-G5*'TYU 1'!$F$15</f>
+        <f>-G5*'Chp 13 TYU 1'!$F$15</f>
         <v>-21.859269120000004</v>
       </c>
       <c r="H6" s="25">
-        <f>-H5*'TYU 1'!$F$15</f>
+        <f>-H5*'Chp 13 TYU 1'!$F$15</f>
         <v>-21.859269120000004</v>
       </c>
     </row>
@@ -1812,23 +2237,23 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="19">
-        <f>'TYU 1'!D20</f>
+        <f>'Chp 13 TYU 1'!D20</f>
         <v>7</v>
       </c>
       <c r="E7" s="8">
-        <f>'TYU 1'!E20</f>
+        <f>'Chp 13 TYU 1'!E20</f>
         <v>8</v>
       </c>
       <c r="F7" s="8">
-        <f>'TYU 1'!F20</f>
+        <f>'Chp 13 TYU 1'!F20</f>
         <v>9</v>
       </c>
       <c r="G7" s="17">
-        <f>'TYU 1'!G20</f>
+        <f>'Chp 13 TYU 1'!G20</f>
         <v>10</v>
       </c>
       <c r="H7" s="28">
-        <f>'TYU 1'!H20</f>
+        <f>'Chp 13 TYU 1'!H20</f>
         <v>10</v>
       </c>
     </row>
@@ -1862,23 +2287,23 @@
         <v>19</v>
       </c>
       <c r="D9" s="13">
-        <f>-'TYU 1'!D22</f>
+        <f>-'Chp 13 TYU 1'!D22</f>
         <v>-7</v>
       </c>
       <c r="E9">
-        <f>-'TYU 1'!E22</f>
+        <f>-'Chp 13 TYU 1'!E22</f>
         <v>-8</v>
       </c>
       <c r="F9">
-        <f>-'TYU 1'!F22</f>
+        <f>-'Chp 13 TYU 1'!F22</f>
         <v>-9</v>
       </c>
       <c r="G9" s="14">
-        <f>-'TYU 1'!G22</f>
+        <f>-'Chp 13 TYU 1'!G22</f>
         <v>-10</v>
       </c>
       <c r="H9" s="27">
-        <f>-'TYU 1'!H22</f>
+        <f>-'Chp 13 TYU 1'!H22</f>
         <v>-10</v>
       </c>
     </row>
@@ -1887,23 +2312,23 @@
         <v>18</v>
       </c>
       <c r="D10" s="20">
-        <f>-(D4-C4)*'TYU 1'!D21</f>
+        <f>-(D4-C4)*'Chp 13 TYU 1'!D21</f>
         <v>-3.2</v>
       </c>
       <c r="E10" s="7">
-        <f>-(E4-D4)*'TYU 1'!E21</f>
+        <f>-(E4-D4)*'Chp 13 TYU 1'!E21</f>
         <v>-1.9439999999999986</v>
       </c>
       <c r="F10" s="7">
-        <f>-(F4-E4)*'TYU 1'!F21</f>
+        <f>-(F4-E4)*'Chp 13 TYU 1'!F21</f>
         <v>-1.3737600000000043</v>
       </c>
       <c r="G10" s="15">
-        <f>-(G4-F4)*'TYU 1'!G21</f>
+        <f>-(G4-F4)*'Chp 13 TYU 1'!G21</f>
         <v>-0.47623680000000151</v>
       </c>
       <c r="H10" s="26">
-        <f>-(H4-G4)*'TYU 1'!H21</f>
+        <f>-(H4-G4)*'Chp 13 TYU 1'!H21</f>
         <v>0</v>
       </c>
     </row>
@@ -1937,19 +2362,19 @@
         <v>23</v>
       </c>
       <c r="D12" s="22">
-        <f>1/(1+'TYU 1'!$J$15)^'Answer 1'!D3</f>
+        <f>1/(1+'Chp 13 TYU 1'!$J$15)^'Answer 1'!D3</f>
         <v>0.86956521739130443</v>
       </c>
       <c r="E12" s="29">
-        <f>1/(1+'TYU 1'!$J$15)^'Answer 1'!E3</f>
+        <f>1/(1+'Chp 13 TYU 1'!$J$15)^'Answer 1'!E3</f>
         <v>0.7561436672967865</v>
       </c>
       <c r="F12" s="29">
-        <f>1/(1+'TYU 1'!$J$15)^'Answer 1'!F3</f>
+        <f>1/(1+'Chp 13 TYU 1'!$J$15)^'Answer 1'!F3</f>
         <v>0.65751623243198831</v>
       </c>
       <c r="G12" s="18">
-        <f>1/(1+'TYU 1'!$J$15)^'Answer 1'!G3</f>
+        <f>1/(1+'Chp 13 TYU 1'!$J$15)^'Answer 1'!G3</f>
         <v>0.57175324559303342</v>
       </c>
       <c r="H12" s="30">
@@ -1996,7 +2421,7 @@
         <v>31</v>
       </c>
       <c r="G15" s="6">
-        <f>H11/'TYU 1'!J15</f>
+        <f>H11/'Chp 13 TYU 1'!J15</f>
         <v>340.03307520000004</v>
       </c>
     </row>
@@ -2006,7 +2431,7 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="11">
-        <f>'TYU 1'!M16</f>
+        <f>'Chp 13 TYU 1'!M16</f>
         <v>4</v>
       </c>
     </row>
@@ -2026,7 +2451,7 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9">
-        <f>-'TYU 1'!M15</f>
+        <f>-'Chp 13 TYU 1'!M15</f>
         <v>-48</v>
       </c>
     </row>
@@ -2678,10 +3103,10 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="71">
+      <c r="C18" s="58">
         <f>SUM(D15:F15)</f>
         <v>786.51165733626317</v>
       </c>
@@ -2712,61 +3137,61 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="63"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="110"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="63"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="110"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="63"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="110"/>
     </row>
     <row r="6" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="66"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="68"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="113"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
@@ -2825,108 +3250,108 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
       <c r="G3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="72">
+      <c r="C4" s="59">
         <v>0</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="59">
         <f>C4+1</f>
         <v>1</v>
       </c>
-      <c r="E4" s="72">
-        <f t="shared" ref="E4:G4" si="0">D4+1</f>
+      <c r="E4" s="59">
+        <f t="shared" ref="E4:F4" si="0">D4+1</f>
         <v>2</v>
       </c>
-      <c r="F4" s="72">
+      <c r="F4" s="59">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G4" s="72">
+      <c r="G4" s="59">
         <f>F4+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="73">
+      <c r="C5" s="60">
         <f>'TYU 3'!$E$8</f>
         <v>0.32</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="60">
         <f>'TYU 3'!$E$8</f>
         <v>0.32</v>
       </c>
-      <c r="E5" s="73">
+      <c r="E5" s="60">
         <f>'TYU 3'!$E$8</f>
         <v>0.32</v>
       </c>
-      <c r="F5" s="73">
+      <c r="F5" s="60">
         <f>'TYU 3'!$E$8</f>
         <v>0.32</v>
       </c>
-      <c r="G5" s="73">
+      <c r="G5" s="60">
         <f>F5*(1+'TYU 3'!D10)</f>
         <v>0.33280000000000004</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="61">
         <f>1/(1+'TYU 3'!$C$9)^'Answer 3'!C4</f>
         <v>1</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="61">
         <f>1/(1+'TYU 3'!$C$9)^'Answer 3'!D4</f>
         <v>0.86206896551724144</v>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="61">
         <f>1/(1+'TYU 3'!$C$9)^'Answer 3'!E4</f>
         <v>0.74316290130796681</v>
       </c>
-      <c r="F6" s="74">
+      <c r="F6" s="61">
         <f>1/(1+'TYU 3'!$C$9)^'Answer 3'!F4</f>
         <v>0.64065767354135073</v>
       </c>
-      <c r="G6" s="74">
+      <c r="G6" s="61">
         <f>F6</f>
         <v>0.64065767354135073</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="62">
         <f>C6*C5</f>
         <v>0.32</v>
       </c>
-      <c r="D7" s="75">
-        <f t="shared" ref="D7:G7" si="1">D6*D5</f>
+      <c r="D7" s="62">
+        <f t="shared" ref="D7:F7" si="1">D6*D5</f>
         <v>0.27586206896551729</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="62">
         <f t="shared" si="1"/>
         <v>0.23781212841854937</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="62">
         <f t="shared" si="1"/>
         <v>0.20501045553323224</v>
       </c>
-      <c r="G7" s="75">
+      <c r="G7" s="62">
         <f>G9*G6</f>
         <v>1.776757281288013</v>
       </c>
@@ -2953,4 +3378,1123 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4522E8-EAE6-427E-98BF-34AD066FF062}">
+  <dimension ref="B2:Q47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="105" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="105"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="118" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="121" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9">
+        <v>840</v>
+      </c>
+      <c r="G9" s="27">
+        <v>830</v>
+      </c>
+      <c r="I9" s="119" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="120"/>
+      <c r="K9" s="91"/>
+      <c r="L9" s="91"/>
+      <c r="M9" s="91"/>
+      <c r="N9" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="O9" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q9" s="93" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10">
+        <v>554</v>
+      </c>
+      <c r="G10" s="27">
+        <v>591</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O10" s="76">
+        <f>F13/F38</f>
+        <v>0.21141649048625794</v>
+      </c>
+      <c r="P10" s="76">
+        <f>G13/G38</f>
+        <v>0.10516605166051661</v>
+      </c>
+      <c r="Q10" s="77">
+        <f>O10-P10</f>
+        <v>0.10625043882574133</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="71" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="64">
+        <f>F9-F10</f>
+        <v>286</v>
+      </c>
+      <c r="G11" s="68">
+        <f>G9-G10</f>
+        <v>239</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="78">
+        <f>F13*(1-$C$16)/F38</f>
+        <v>0.10570824524312897</v>
+      </c>
+      <c r="P11" s="78">
+        <f>G13*(1-$C$16)/G38</f>
+        <v>5.2583025830258305E-2</v>
+      </c>
+      <c r="Q11" s="79">
+        <f>O11-P11</f>
+        <v>5.3125219412870663E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12">
+        <v>186</v>
+      </c>
+      <c r="G12" s="27">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="64">
+        <f>F11-F12</f>
+        <v>100</v>
+      </c>
+      <c r="G13" s="68">
+        <f>G11-G12</f>
+        <v>57</v>
+      </c>
+      <c r="I13" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" s="91"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="O13" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="P13" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q13" s="93" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14" s="27">
+        <v>8</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="N14" t="s">
+        <v>107</v>
+      </c>
+      <c r="O14" s="80">
+        <f>(F27/F9)*365</f>
+        <v>45.625</v>
+      </c>
+      <c r="P14" s="80">
+        <f>(G27/G9)*365</f>
+        <v>58.048192771084338</v>
+      </c>
+      <c r="Q14" s="81">
+        <f>O14-P14</f>
+        <v>-12.423192771084338</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B15" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="64">
+        <f>F13-F14</f>
+        <v>94</v>
+      </c>
+      <c r="G15" s="68">
+        <f>G13-G14</f>
+        <v>49</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="N15" t="s">
+        <v>107</v>
+      </c>
+      <c r="O15" s="80">
+        <f>(F40/F10)*365</f>
+        <v>87.62635379061372</v>
+      </c>
+      <c r="P15" s="80">
+        <f>(G40/G10)*365</f>
+        <v>75.346869712351946</v>
+      </c>
+      <c r="Q15" s="81">
+        <f t="shared" ref="Q15:Q17" si="0">O15-P15</f>
+        <v>12.279484078261774</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B16" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="F16">
+        <f>F15*50%</f>
+        <v>47</v>
+      </c>
+      <c r="G16" s="27">
+        <f>G15*50%</f>
+        <v>24.5</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="N16" t="s">
+        <v>107</v>
+      </c>
+      <c r="O16" s="80">
+        <f>(F26/F10)*365</f>
+        <v>156.14620938628158</v>
+      </c>
+      <c r="P16" s="80">
+        <f>(G26/G10)*365</f>
+        <v>163.66328257191199</v>
+      </c>
+      <c r="Q16" s="81">
+        <f t="shared" si="0"/>
+        <v>-7.5170731856304087</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="69">
+        <f>F15-F16</f>
+        <v>47</v>
+      </c>
+      <c r="G17" s="70">
+        <f>G15-G16</f>
+        <v>24.5</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="O17" s="82">
+        <f>O14+O16-O15</f>
+        <v>114.14485559566786</v>
+      </c>
+      <c r="P17" s="82">
+        <f>P14+P16-P15</f>
+        <v>146.36460563064438</v>
+      </c>
+      <c r="Q17" s="83">
+        <f t="shared" si="0"/>
+        <v>-32.219750034976514</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" s="123" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="J19" s="91"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="O19" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q19" s="93" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="121" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="O20" s="76">
+        <f>F37/F35</f>
+        <v>0.18546365914786966</v>
+      </c>
+      <c r="P20" s="76">
+        <f>G37/G35</f>
+        <v>0.20982142857142858</v>
+      </c>
+      <c r="Q20" s="77">
+        <f>O20-P20</f>
+        <v>-2.4357769423558912E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B21" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="27"/>
+      <c r="I21" s="125" t="s">
+        <v>111</v>
+      </c>
+      <c r="J21" s="126"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="O21" s="82">
+        <f>F13/F14</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="P21" s="82">
+        <f>G13/G14</f>
+        <v>7.125</v>
+      </c>
+      <c r="Q21" s="83">
+        <f t="shared" ref="Q21:Q26" si="1">O21-P21</f>
+        <v>9.5416666666666679</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22">
+        <v>36</v>
+      </c>
+      <c r="G22" s="27">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="75"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23">
+        <v>176</v>
+      </c>
+      <c r="G23" s="27">
+        <v>222</v>
+      </c>
+      <c r="I23" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="O23" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="P23" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q23" s="93" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="24"/>
+      <c r="F24" s="64">
+        <f>SUM(F22:F23)</f>
+        <v>212</v>
+      </c>
+      <c r="G24" s="68">
+        <f>SUM(G22:G23)</f>
+        <v>254</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="56">
+        <f>F43</f>
+        <v>1.6</v>
+      </c>
+      <c r="P24" s="56">
+        <f>G43</f>
+        <v>0.8</v>
+      </c>
+      <c r="Q24" s="84">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B25" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="27"/>
+      <c r="I25" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="O25" s="56">
+        <f>O24/O26</f>
+        <v>6.8085106382978733</v>
+      </c>
+      <c r="P25" s="56">
+        <f>P24/P26</f>
+        <v>6.5306122448979593</v>
+      </c>
+      <c r="Q25" s="85">
+        <f t="shared" si="1"/>
+        <v>0.27789839339991396</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B26" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26">
+        <v>237</v>
+      </c>
+      <c r="G26" s="27">
+        <v>265</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="86">
+        <f>(F17*1000000)/$L$29</f>
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="P26" s="86">
+        <f>(G17*1000000)/$L$29</f>
+        <v>0.1225</v>
+      </c>
+      <c r="Q26" s="87">
+        <f t="shared" si="1"/>
+        <v>0.11249999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27">
+        <v>105</v>
+      </c>
+      <c r="G27" s="27">
+        <v>132</v>
+      </c>
+      <c r="Q27" s="75"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28">
+        <v>52</v>
+      </c>
+      <c r="G28" s="27">
+        <v>13</v>
+      </c>
+      <c r="Q28" s="75"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="24"/>
+      <c r="F29" s="64">
+        <f>SUM(F26:F28)</f>
+        <v>394</v>
+      </c>
+      <c r="G29" s="68">
+        <f>SUM(G26:G28)</f>
+        <v>410</v>
+      </c>
+      <c r="I29" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="L29">
+        <f>(F33*1000000)/D33</f>
+        <v>200000000</v>
+      </c>
+      <c r="M29" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q29" s="75"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B30" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="65">
+        <f>F24+F29</f>
+        <v>606</v>
+      </c>
+      <c r="G30" s="74">
+        <f>G24+G29</f>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B31" s="24"/>
+      <c r="G31" s="27"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B32" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="27"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33">
+        <v>0.5</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33" s="27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34">
+        <v>299</v>
+      </c>
+      <c r="G34" s="27">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="24"/>
+      <c r="F35" s="64">
+        <f>SUM(F33:F34)</f>
+        <v>399</v>
+      </c>
+      <c r="G35" s="68">
+        <f>SUM(G33:G34)</f>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="71" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" s="27"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37">
+        <v>74</v>
+      </c>
+      <c r="G37" s="27">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="24"/>
+      <c r="F38" s="64">
+        <f>F35+F37</f>
+        <v>473</v>
+      </c>
+      <c r="G38" s="68">
+        <f>G35+G37</f>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="71" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" s="27"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40">
+        <v>133</v>
+      </c>
+      <c r="G40" s="27">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="69">
+        <f>F38+F40</f>
+        <v>606</v>
+      </c>
+      <c r="G41" s="70">
+        <f>G38+G40</f>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="F43" s="56">
+        <v>1.6</v>
+      </c>
+      <c r="G43" s="56">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="124" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="124"/>
+      <c r="D45" s="124"/>
+      <c r="E45" s="124"/>
+      <c r="F45" s="124"/>
+      <c r="G45" s="124"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B46" s="124"/>
+      <c r="C46" s="124"/>
+      <c r="D46" s="124"/>
+      <c r="E46" s="124"/>
+      <c r="F46" s="124"/>
+      <c r="G46" s="124"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="124"/>
+      <c r="C47" s="124"/>
+      <c r="D47" s="124"/>
+      <c r="E47" s="124"/>
+      <c r="F47" s="124"/>
+      <c r="G47" s="124"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B45:G47"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:H5"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A18:XFD18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFFD9EC-5332-4BD6-A57D-C997D0AD6483}">
+  <dimension ref="B7:J38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="2:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="B7" s="88" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="105" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+    </row>
+    <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="104" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="63" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="27"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="89">
+        <v>193246</v>
+      </c>
+      <c r="E14" s="96">
+        <f>80000+80000</f>
+        <v>160000</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="89">
+        <f>E22</f>
+        <v>363622.8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="89">
+        <v>60754</v>
+      </c>
+      <c r="E15" s="27">
+        <v>30000</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="89">
+        <v>27000</v>
+      </c>
+      <c r="E16" s="96">
+        <v>60000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="89">
+        <f>-D31</f>
+        <v>-80000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="24"/>
+      <c r="D17" s="90">
+        <f>SUM(D14:D16)</f>
+        <v>281000</v>
+      </c>
+      <c r="E17" s="97">
+        <f>SUM(E14:E16)</f>
+        <v>250000</v>
+      </c>
+      <c r="H17" s="90">
+        <f>SUM(H14:H16)</f>
+        <v>283622.8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="27"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="89">
+        <v>120247</v>
+      </c>
+      <c r="E19" s="27">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="89">
+        <v>70692</v>
+      </c>
+      <c r="E20" s="98">
+        <f>D20*90%</f>
+        <v>63622.8</v>
+      </c>
+      <c r="G20" s="63" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="24"/>
+      <c r="D21" s="90">
+        <f>SUM(D19:D20)</f>
+        <v>190939</v>
+      </c>
+      <c r="E21" s="97">
+        <f>SUM(E19:E20)</f>
+        <v>113622.8</v>
+      </c>
+      <c r="G21" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21" s="89">
+        <f>D34</f>
+        <v>112247</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="95">
+        <f>D17+D21</f>
+        <v>471939</v>
+      </c>
+      <c r="E22" s="99">
+        <f>E17+E21</f>
+        <v>363622.8</v>
+      </c>
+      <c r="G22" t="s">
+        <v>136</v>
+      </c>
+      <c r="H22" s="89">
+        <f t="shared" ref="H22:H23" si="0">D35</f>
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="24"/>
+      <c r="E23" s="27"/>
+      <c r="G23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="89">
+        <f t="shared" si="0"/>
+        <v>36713</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="27"/>
+      <c r="G24" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" s="95">
+        <f>H17-SUM(H21:H23)</f>
+        <v>121862.79999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="89">
+        <v>200000</v>
+      </c>
+      <c r="E25" s="27"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="89">
+        <v>70000</v>
+      </c>
+      <c r="E26" s="27"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="89">
+        <v>-39821</v>
+      </c>
+      <c r="E27" s="27"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="24"/>
+      <c r="D28" s="90">
+        <f>SUM(D25:D27)</f>
+        <v>230179</v>
+      </c>
+      <c r="E28" s="27"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="24"/>
+      <c r="E29" s="27"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="71" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="27"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="89">
+        <v>80000</v>
+      </c>
+      <c r="E31" s="27"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="24"/>
+      <c r="E32" s="27"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="27"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="89">
+        <v>112247</v>
+      </c>
+      <c r="E34" s="27"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="89">
+        <v>12800</v>
+      </c>
+      <c r="E35" s="27"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="89">
+        <v>36713</v>
+      </c>
+      <c r="E36" s="27"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="24"/>
+      <c r="D37" s="90">
+        <f>SUM(D34:D36)</f>
+        <v>161760</v>
+      </c>
+      <c r="E37" s="27"/>
+    </row>
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="100">
+        <f>D28+D31+D37</f>
+        <v>471939</v>
+      </c>
+      <c r="E38" s="101"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B9:J10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>